--- a/data/salidafca.xlsx
+++ b/data/salidafca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\ARedecillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81A750D8-0C2A-4DC2-BD4F-91886489A2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374378F9-34A5-4D2D-9CCD-2E74FF377D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9D74F18-6806-4A2B-AA7D-1324A847848B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D9D74F18-6806-4A2B-AA7D-1324A847848B}"/>
   </bookViews>
   <sheets>
     <sheet name="salidafca" sheetId="1" r:id="rId1"/>
@@ -38,12 +38,25 @@
     <definedName name="UNI_RET_UNIT" hidden="1">2</definedName>
     <definedName name="UNI_RET_VALUE" hidden="1">16</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="47">
   <si>
     <t>pagina</t>
   </si>
@@ -629,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD8619E-C23C-43D2-9AC7-2D7E3DE8CE25}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1189,6 +1202,4989 @@
       </c>
       <c r="E26">
         <v>4</v>
+      </c>
+      <c r="G26">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <v>1420260043</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46036</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28">
+        <v>1420260044</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46037</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29">
+        <v>1420260045</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46038</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>1420260046</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46039</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>1420260047</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46040</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32">
+        <v>1420260048</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46041</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33">
+        <v>1420260049</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>1420260050</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46043</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>1420260051</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46044</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>1420260052</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46045</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>1420260053</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>1420260054</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46047</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39">
+        <v>1420260055</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46048</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40">
+        <v>1420260056</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41">
+        <v>1420260057</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46050</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>1420260058</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46051</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="G42">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>1420260059</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44">
+        <v>1420260060</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46053</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45">
+        <v>1420260061</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46">
+        <v>1420260062</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46055</v>
+      </c>
+      <c r="D46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47">
+        <v>1420260063</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <v>1420260064</v>
+      </c>
+      <c r="C48" s="1">
+        <v>46057</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="G48">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <v>1420260065</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46058</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="G49">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <v>1420260066</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46059</v>
+      </c>
+      <c r="D50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51">
+        <v>1420260067</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46060</v>
+      </c>
+      <c r="D51" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52">
+        <v>1420260068</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46061</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53">
+        <v>1420260069</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46062</v>
+      </c>
+      <c r="D53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54">
+        <v>1420260070</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46063</v>
+      </c>
+      <c r="D54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55">
+        <v>1420260071</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46064</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56">
+        <v>1420260072</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D56" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57">
+        <v>1420260073</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46066</v>
+      </c>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58">
+        <v>1420260074</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46067</v>
+      </c>
+      <c r="D58" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59">
+        <v>1420260075</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46068</v>
+      </c>
+      <c r="D59" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60">
+        <v>1420260076</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61">
+        <v>1420260077</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46070</v>
+      </c>
+      <c r="D61" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>0</v>
+      </c>
+      <c r="B62">
+        <v>1420260078</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46071</v>
+      </c>
+      <c r="D62" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>0</v>
+      </c>
+      <c r="B63">
+        <v>1420260079</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46072</v>
+      </c>
+      <c r="D63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>0</v>
+      </c>
+      <c r="B64">
+        <v>1420260080</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46073</v>
+      </c>
+      <c r="D64" t="s">
+        <v>46</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="G64">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>0</v>
+      </c>
+      <c r="B65">
+        <v>1420260081</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46074</v>
+      </c>
+      <c r="D65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>0</v>
+      </c>
+      <c r="B66">
+        <v>1420260082</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46075</v>
+      </c>
+      <c r="D66" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>0</v>
+      </c>
+      <c r="B67">
+        <v>1420260083</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46076</v>
+      </c>
+      <c r="D67" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>0</v>
+      </c>
+      <c r="B68">
+        <v>1420260084</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46077</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68">
+        <v>5</v>
+      </c>
+      <c r="G68">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>0</v>
+      </c>
+      <c r="B69">
+        <v>1420260085</v>
+      </c>
+      <c r="C69" s="1">
+        <v>46078</v>
+      </c>
+      <c r="D69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>0</v>
+      </c>
+      <c r="B70">
+        <v>1420260086</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46079</v>
+      </c>
+      <c r="D70" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>0</v>
+      </c>
+      <c r="B71">
+        <v>1420260087</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46080</v>
+      </c>
+      <c r="D71" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>0</v>
+      </c>
+      <c r="B72">
+        <v>1420260088</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46081</v>
+      </c>
+      <c r="D72" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="G72">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>0</v>
+      </c>
+      <c r="B73">
+        <v>1420260089</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46082</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>0</v>
+      </c>
+      <c r="B74">
+        <v>1420260090</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46083</v>
+      </c>
+      <c r="D74" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74">
+        <v>5</v>
+      </c>
+      <c r="G74">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>0</v>
+      </c>
+      <c r="B75">
+        <v>1420260091</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46084</v>
+      </c>
+      <c r="D75" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="B76">
+        <v>1420260092</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46085</v>
+      </c>
+      <c r="D76" t="s">
+        <v>46</v>
+      </c>
+      <c r="E76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="B77">
+        <v>1420260093</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46086</v>
+      </c>
+      <c r="D77" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>0</v>
+      </c>
+      <c r="B78">
+        <v>1420260094</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46087</v>
+      </c>
+      <c r="D78" t="s">
+        <v>46</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="G78">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="B79">
+        <v>1420260095</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46088</v>
+      </c>
+      <c r="D79" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="G79">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>0</v>
+      </c>
+      <c r="B80">
+        <v>1420260096</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46089</v>
+      </c>
+      <c r="D80" t="s">
+        <v>46</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>0</v>
+      </c>
+      <c r="B81">
+        <v>1420260097</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="G81">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>0</v>
+      </c>
+      <c r="B82">
+        <v>1420260098</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46091</v>
+      </c>
+      <c r="D82" t="s">
+        <v>46</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>0</v>
+      </c>
+      <c r="B83">
+        <v>1420260099</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46092</v>
+      </c>
+      <c r="D83" t="s">
+        <v>46</v>
+      </c>
+      <c r="E83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>0</v>
+      </c>
+      <c r="B84">
+        <v>1420260100</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D84" t="s">
+        <v>46</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="B85">
+        <v>1420260101</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D85" t="s">
+        <v>46</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="G85">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>0</v>
+      </c>
+      <c r="B86">
+        <v>1420260102</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46095</v>
+      </c>
+      <c r="D86" t="s">
+        <v>46</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+      <c r="G86">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>0</v>
+      </c>
+      <c r="B87">
+        <v>1420260103</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46096</v>
+      </c>
+      <c r="D87" t="s">
+        <v>46</v>
+      </c>
+      <c r="E87">
+        <v>4</v>
+      </c>
+      <c r="G87">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>0</v>
+      </c>
+      <c r="B88">
+        <v>1420260104</v>
+      </c>
+      <c r="C88" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D88" t="s">
+        <v>46</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>0</v>
+      </c>
+      <c r="B89">
+        <v>1420260105</v>
+      </c>
+      <c r="C89" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="G89">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>0</v>
+      </c>
+      <c r="B90">
+        <v>1420260106</v>
+      </c>
+      <c r="C90" s="1">
+        <v>46099</v>
+      </c>
+      <c r="D90" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90">
+        <v>4</v>
+      </c>
+      <c r="G90">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>0</v>
+      </c>
+      <c r="B91">
+        <v>1420260107</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46100</v>
+      </c>
+      <c r="D91" t="s">
+        <v>46</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92">
+        <v>1420260108</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D92" t="s">
+        <v>46</v>
+      </c>
+      <c r="E92">
+        <v>4</v>
+      </c>
+      <c r="G92">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>0</v>
+      </c>
+      <c r="B93">
+        <v>1420260109</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46102</v>
+      </c>
+      <c r="D93" t="s">
+        <v>46</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>0</v>
+      </c>
+      <c r="B94">
+        <v>1420260110</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46103</v>
+      </c>
+      <c r="D94" t="s">
+        <v>46</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="G94">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>0</v>
+      </c>
+      <c r="B95">
+        <v>1420260111</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46104</v>
+      </c>
+      <c r="D95" t="s">
+        <v>46</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>0</v>
+      </c>
+      <c r="B96">
+        <v>1420260112</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D96" t="s">
+        <v>46</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>0</v>
+      </c>
+      <c r="B97">
+        <v>1420260113</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>46</v>
+      </c>
+      <c r="E97">
+        <v>4</v>
+      </c>
+      <c r="G97">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>0</v>
+      </c>
+      <c r="B98">
+        <v>1420260114</v>
+      </c>
+      <c r="C98" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D98" t="s">
+        <v>46</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="G98">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99">
+        <v>1420260115</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D99" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+      <c r="G99">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100">
+        <v>1420260116</v>
+      </c>
+      <c r="C100" s="1">
+        <v>46109</v>
+      </c>
+      <c r="D100" t="s">
+        <v>46</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="G100">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>0</v>
+      </c>
+      <c r="B101">
+        <v>1420260117</v>
+      </c>
+      <c r="C101" s="1">
+        <v>46110</v>
+      </c>
+      <c r="D101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>0</v>
+      </c>
+      <c r="B102">
+        <v>1420260118</v>
+      </c>
+      <c r="C102" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D102" t="s">
+        <v>46</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="G102">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>0</v>
+      </c>
+      <c r="B103">
+        <v>1420260119</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D103" t="s">
+        <v>46</v>
+      </c>
+      <c r="E103">
+        <v>3</v>
+      </c>
+      <c r="G103">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>0</v>
+      </c>
+      <c r="B104">
+        <v>1420260120</v>
+      </c>
+      <c r="C104" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D104" t="s">
+        <v>46</v>
+      </c>
+      <c r="E104">
+        <v>5</v>
+      </c>
+      <c r="G104">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>0</v>
+      </c>
+      <c r="B105">
+        <v>1420260121</v>
+      </c>
+      <c r="C105" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D105" t="s">
+        <v>46</v>
+      </c>
+      <c r="E105">
+        <v>4</v>
+      </c>
+      <c r="G105">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>0</v>
+      </c>
+      <c r="B106">
+        <v>1420260122</v>
+      </c>
+      <c r="C106" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D106" t="s">
+        <v>46</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+      <c r="G106">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>0</v>
+      </c>
+      <c r="B107">
+        <v>1420260123</v>
+      </c>
+      <c r="C107" s="1">
+        <v>46116</v>
+      </c>
+      <c r="D107" t="s">
+        <v>46</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>0</v>
+      </c>
+      <c r="B108">
+        <v>1420260124</v>
+      </c>
+      <c r="C108" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D108" t="s">
+        <v>46</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>0</v>
+      </c>
+      <c r="B109">
+        <v>1420260125</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D109" t="s">
+        <v>46</v>
+      </c>
+      <c r="E109">
+        <v>3</v>
+      </c>
+      <c r="G109">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>0</v>
+      </c>
+      <c r="B110">
+        <v>1420260126</v>
+      </c>
+      <c r="C110" s="1">
+        <v>46119</v>
+      </c>
+      <c r="D110" t="s">
+        <v>46</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>0</v>
+      </c>
+      <c r="B111">
+        <v>1420260127</v>
+      </c>
+      <c r="C111" s="1">
+        <v>46120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>46</v>
+      </c>
+      <c r="E111">
+        <v>5</v>
+      </c>
+      <c r="G111">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>0</v>
+      </c>
+      <c r="B112">
+        <v>1420260128</v>
+      </c>
+      <c r="C112" s="1">
+        <v>46121</v>
+      </c>
+      <c r="D112" t="s">
+        <v>46</v>
+      </c>
+      <c r="E112">
+        <v>3</v>
+      </c>
+      <c r="G112">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>0</v>
+      </c>
+      <c r="B113">
+        <v>1420260129</v>
+      </c>
+      <c r="C113" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D113" t="s">
+        <v>46</v>
+      </c>
+      <c r="E113">
+        <v>4</v>
+      </c>
+      <c r="G113">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>0</v>
+      </c>
+      <c r="B114">
+        <v>1420260130</v>
+      </c>
+      <c r="C114" s="1">
+        <v>46123</v>
+      </c>
+      <c r="D114" t="s">
+        <v>46</v>
+      </c>
+      <c r="E114">
+        <v>5</v>
+      </c>
+      <c r="G114">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>0</v>
+      </c>
+      <c r="B115">
+        <v>1420260131</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46124</v>
+      </c>
+      <c r="D115" t="s">
+        <v>46</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="G115">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>0</v>
+      </c>
+      <c r="B116">
+        <v>1420260132</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D116" t="s">
+        <v>46</v>
+      </c>
+      <c r="E116">
+        <v>3</v>
+      </c>
+      <c r="G116">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>0</v>
+      </c>
+      <c r="B117">
+        <v>1420260133</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D117" t="s">
+        <v>46</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>0</v>
+      </c>
+      <c r="B118">
+        <v>1420260134</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46127</v>
+      </c>
+      <c r="D118" t="s">
+        <v>46</v>
+      </c>
+      <c r="E118">
+        <v>5</v>
+      </c>
+      <c r="G118">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>0</v>
+      </c>
+      <c r="B119">
+        <v>1420260135</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46128</v>
+      </c>
+      <c r="D119" t="s">
+        <v>46</v>
+      </c>
+      <c r="E119">
+        <v>3</v>
+      </c>
+      <c r="G119">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>0</v>
+      </c>
+      <c r="B120">
+        <v>1420260136</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46129</v>
+      </c>
+      <c r="D120" t="s">
+        <v>46</v>
+      </c>
+      <c r="E120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>0</v>
+      </c>
+      <c r="B121">
+        <v>1420260137</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46130</v>
+      </c>
+      <c r="D121" t="s">
+        <v>46</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+      <c r="G121">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>0</v>
+      </c>
+      <c r="B122">
+        <v>1420260138</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46131</v>
+      </c>
+      <c r="D122" t="s">
+        <v>46</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="G122">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>0</v>
+      </c>
+      <c r="B123">
+        <v>1420260139</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D123" t="s">
+        <v>46</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="G123">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>0</v>
+      </c>
+      <c r="B124">
+        <v>1420260140</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D124" t="s">
+        <v>46</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>0</v>
+      </c>
+      <c r="B125">
+        <v>1420260141</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46134</v>
+      </c>
+      <c r="D125" t="s">
+        <v>46</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="G125">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>0</v>
+      </c>
+      <c r="B126">
+        <v>1420260142</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46135</v>
+      </c>
+      <c r="D126" t="s">
+        <v>46</v>
+      </c>
+      <c r="E126">
+        <v>5</v>
+      </c>
+      <c r="G126">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>0</v>
+      </c>
+      <c r="B127">
+        <v>1420260143</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D127" t="s">
+        <v>46</v>
+      </c>
+      <c r="E127">
+        <v>4</v>
+      </c>
+      <c r="G127">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>0</v>
+      </c>
+      <c r="B128">
+        <v>1420260144</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46137</v>
+      </c>
+      <c r="D128" t="s">
+        <v>46</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>0</v>
+      </c>
+      <c r="B129">
+        <v>1420260145</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46138</v>
+      </c>
+      <c r="D129" t="s">
+        <v>46</v>
+      </c>
+      <c r="E129">
+        <v>3</v>
+      </c>
+      <c r="G129">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>0</v>
+      </c>
+      <c r="B130">
+        <v>1420260146</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46139</v>
+      </c>
+      <c r="D130" t="s">
+        <v>46</v>
+      </c>
+      <c r="E130">
+        <v>4</v>
+      </c>
+      <c r="G130">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>0</v>
+      </c>
+      <c r="B131">
+        <v>1420260147</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46140</v>
+      </c>
+      <c r="D131" t="s">
+        <v>46</v>
+      </c>
+      <c r="E131">
+        <v>3</v>
+      </c>
+      <c r="G131">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>0</v>
+      </c>
+      <c r="B132">
+        <v>1420260148</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D132" t="s">
+        <v>46</v>
+      </c>
+      <c r="E132">
+        <v>4</v>
+      </c>
+      <c r="G132">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>0</v>
+      </c>
+      <c r="B133">
+        <v>1420260149</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46142</v>
+      </c>
+      <c r="D133" t="s">
+        <v>46</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="G133">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>0</v>
+      </c>
+      <c r="B134">
+        <v>1420260150</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D134" t="s">
+        <v>46</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="G134">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>0</v>
+      </c>
+      <c r="B135">
+        <v>1420260151</v>
+      </c>
+      <c r="C135" s="1">
+        <v>46144</v>
+      </c>
+      <c r="D135" t="s">
+        <v>46</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>0</v>
+      </c>
+      <c r="B136">
+        <v>1420260152</v>
+      </c>
+      <c r="C136" s="1">
+        <v>46145</v>
+      </c>
+      <c r="D136" t="s">
+        <v>46</v>
+      </c>
+      <c r="E136">
+        <v>4</v>
+      </c>
+      <c r="G136">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>0</v>
+      </c>
+      <c r="B137">
+        <v>1420260153</v>
+      </c>
+      <c r="C137" s="1">
+        <v>46146</v>
+      </c>
+      <c r="D137" t="s">
+        <v>46</v>
+      </c>
+      <c r="E137">
+        <v>5</v>
+      </c>
+      <c r="G137">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>0</v>
+      </c>
+      <c r="B138">
+        <v>1420260154</v>
+      </c>
+      <c r="C138" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D138" t="s">
+        <v>46</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="G138">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>0</v>
+      </c>
+      <c r="B139">
+        <v>1420260155</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46148</v>
+      </c>
+      <c r="D139" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139">
+        <v>5</v>
+      </c>
+      <c r="G139">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>0</v>
+      </c>
+      <c r="B140">
+        <v>1420260156</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46149</v>
+      </c>
+      <c r="D140" t="s">
+        <v>46</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>0</v>
+      </c>
+      <c r="B141">
+        <v>1420260157</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D141" t="s">
+        <v>46</v>
+      </c>
+      <c r="E141">
+        <v>2</v>
+      </c>
+      <c r="G141">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>0</v>
+      </c>
+      <c r="B142">
+        <v>1420260158</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46151</v>
+      </c>
+      <c r="D142" t="s">
+        <v>46</v>
+      </c>
+      <c r="E142">
+        <v>5</v>
+      </c>
+      <c r="G142">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>0</v>
+      </c>
+      <c r="B143">
+        <v>1420260159</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46152</v>
+      </c>
+      <c r="D143" t="s">
+        <v>46</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>0</v>
+      </c>
+      <c r="B144">
+        <v>1420260160</v>
+      </c>
+      <c r="C144" s="1">
+        <v>46153</v>
+      </c>
+      <c r="D144" t="s">
+        <v>46</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>0</v>
+      </c>
+      <c r="B145">
+        <v>1420260161</v>
+      </c>
+      <c r="C145" s="1">
+        <v>46154</v>
+      </c>
+      <c r="D145" t="s">
+        <v>46</v>
+      </c>
+      <c r="E145">
+        <v>4</v>
+      </c>
+      <c r="G145">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>0</v>
+      </c>
+      <c r="B146">
+        <v>1420260162</v>
+      </c>
+      <c r="C146" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D146" t="s">
+        <v>46</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>0</v>
+      </c>
+      <c r="B147">
+        <v>1420260163</v>
+      </c>
+      <c r="C147" s="1">
+        <v>46156</v>
+      </c>
+      <c r="D147" t="s">
+        <v>46</v>
+      </c>
+      <c r="E147">
+        <v>3</v>
+      </c>
+      <c r="G147">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>0</v>
+      </c>
+      <c r="B148">
+        <v>1420260164</v>
+      </c>
+      <c r="C148" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D148" t="s">
+        <v>46</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>0</v>
+      </c>
+      <c r="B149">
+        <v>1420260165</v>
+      </c>
+      <c r="C149" s="1">
+        <v>46158</v>
+      </c>
+      <c r="D149" t="s">
+        <v>46</v>
+      </c>
+      <c r="E149">
+        <v>3</v>
+      </c>
+      <c r="G149">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>0</v>
+      </c>
+      <c r="B150">
+        <v>1420260166</v>
+      </c>
+      <c r="C150" s="1">
+        <v>46159</v>
+      </c>
+      <c r="D150" t="s">
+        <v>46</v>
+      </c>
+      <c r="E150">
+        <v>3</v>
+      </c>
+      <c r="G150">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>0</v>
+      </c>
+      <c r="B151">
+        <v>1420260167</v>
+      </c>
+      <c r="C151" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D151" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="G151">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>0</v>
+      </c>
+      <c r="B152">
+        <v>1420260168</v>
+      </c>
+      <c r="C152" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D152" t="s">
+        <v>46</v>
+      </c>
+      <c r="E152">
+        <v>2</v>
+      </c>
+      <c r="G152">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>0</v>
+      </c>
+      <c r="B153">
+        <v>1420260169</v>
+      </c>
+      <c r="C153" s="1">
+        <v>46162</v>
+      </c>
+      <c r="D153" t="s">
+        <v>46</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>0</v>
+      </c>
+      <c r="B154">
+        <v>1420260170</v>
+      </c>
+      <c r="C154" s="1">
+        <v>46163</v>
+      </c>
+      <c r="D154" t="s">
+        <v>46</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="G154">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>0</v>
+      </c>
+      <c r="B155">
+        <v>1420260171</v>
+      </c>
+      <c r="C155" s="1">
+        <v>46164</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155">
+        <v>5</v>
+      </c>
+      <c r="G155">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>0</v>
+      </c>
+      <c r="B156">
+        <v>1420260172</v>
+      </c>
+      <c r="C156" s="1">
+        <v>46165</v>
+      </c>
+      <c r="D156" t="s">
+        <v>46</v>
+      </c>
+      <c r="E156">
+        <v>5</v>
+      </c>
+      <c r="G156">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>0</v>
+      </c>
+      <c r="B157">
+        <v>1420260173</v>
+      </c>
+      <c r="C157" s="1">
+        <v>46166</v>
+      </c>
+      <c r="D157" t="s">
+        <v>46</v>
+      </c>
+      <c r="E157">
+        <v>5</v>
+      </c>
+      <c r="G157">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>0</v>
+      </c>
+      <c r="B158">
+        <v>1420260174</v>
+      </c>
+      <c r="C158" s="1">
+        <v>46167</v>
+      </c>
+      <c r="D158" t="s">
+        <v>46</v>
+      </c>
+      <c r="E158">
+        <v>2</v>
+      </c>
+      <c r="G158">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>0</v>
+      </c>
+      <c r="B159">
+        <v>1420260175</v>
+      </c>
+      <c r="C159" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D159" t="s">
+        <v>46</v>
+      </c>
+      <c r="E159">
+        <v>3</v>
+      </c>
+      <c r="G159">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>0</v>
+      </c>
+      <c r="B160">
+        <v>1420260176</v>
+      </c>
+      <c r="C160" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D160" t="s">
+        <v>46</v>
+      </c>
+      <c r="E160">
+        <v>3</v>
+      </c>
+      <c r="G160">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>0</v>
+      </c>
+      <c r="B161">
+        <v>1420260177</v>
+      </c>
+      <c r="C161" s="1">
+        <v>46170</v>
+      </c>
+      <c r="D161" t="s">
+        <v>46</v>
+      </c>
+      <c r="E161">
+        <v>3</v>
+      </c>
+      <c r="G161">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>0</v>
+      </c>
+      <c r="B162">
+        <v>1420260178</v>
+      </c>
+      <c r="C162" s="1">
+        <v>46171</v>
+      </c>
+      <c r="D162" t="s">
+        <v>46</v>
+      </c>
+      <c r="E162">
+        <v>2</v>
+      </c>
+      <c r="G162">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>0</v>
+      </c>
+      <c r="B163">
+        <v>1420260179</v>
+      </c>
+      <c r="C163" s="1">
+        <v>46172</v>
+      </c>
+      <c r="D163" t="s">
+        <v>46</v>
+      </c>
+      <c r="E163">
+        <v>4</v>
+      </c>
+      <c r="G163">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>0</v>
+      </c>
+      <c r="B164">
+        <v>1420260180</v>
+      </c>
+      <c r="C164" s="1">
+        <v>46173</v>
+      </c>
+      <c r="D164" t="s">
+        <v>46</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>0</v>
+      </c>
+      <c r="B165">
+        <v>1420260181</v>
+      </c>
+      <c r="C165" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D165" t="s">
+        <v>46</v>
+      </c>
+      <c r="E165">
+        <v>3</v>
+      </c>
+      <c r="G165">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>0</v>
+      </c>
+      <c r="B166">
+        <v>1420260182</v>
+      </c>
+      <c r="C166" s="1">
+        <v>46175</v>
+      </c>
+      <c r="D166" t="s">
+        <v>46</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="G166">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>0</v>
+      </c>
+      <c r="B167">
+        <v>1420260183</v>
+      </c>
+      <c r="C167" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D167" t="s">
+        <v>46</v>
+      </c>
+      <c r="E167">
+        <v>5</v>
+      </c>
+      <c r="G167">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>0</v>
+      </c>
+      <c r="B168">
+        <v>1420260184</v>
+      </c>
+      <c r="C168" s="1">
+        <v>46177</v>
+      </c>
+      <c r="D168" t="s">
+        <v>46</v>
+      </c>
+      <c r="E168">
+        <v>3</v>
+      </c>
+      <c r="G168">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>0</v>
+      </c>
+      <c r="B169">
+        <v>1420260185</v>
+      </c>
+      <c r="C169" s="1">
+        <v>46178</v>
+      </c>
+      <c r="D169" t="s">
+        <v>46</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>0</v>
+      </c>
+      <c r="B170">
+        <v>1420260186</v>
+      </c>
+      <c r="C170" s="1">
+        <v>46179</v>
+      </c>
+      <c r="D170" t="s">
+        <v>46</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>0</v>
+      </c>
+      <c r="B171">
+        <v>1420260187</v>
+      </c>
+      <c r="C171" s="1">
+        <v>46180</v>
+      </c>
+      <c r="D171" t="s">
+        <v>46</v>
+      </c>
+      <c r="E171">
+        <v>5</v>
+      </c>
+      <c r="G171">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>0</v>
+      </c>
+      <c r="B172">
+        <v>1420260188</v>
+      </c>
+      <c r="C172" s="1">
+        <v>46181</v>
+      </c>
+      <c r="D172" t="s">
+        <v>46</v>
+      </c>
+      <c r="E172">
+        <v>3</v>
+      </c>
+      <c r="G172">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>0</v>
+      </c>
+      <c r="B173">
+        <v>1420260189</v>
+      </c>
+      <c r="C173" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D173" t="s">
+        <v>46</v>
+      </c>
+      <c r="E173">
+        <v>3</v>
+      </c>
+      <c r="G173">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>0</v>
+      </c>
+      <c r="B174">
+        <v>1420260190</v>
+      </c>
+      <c r="C174" s="1">
+        <v>46183</v>
+      </c>
+      <c r="D174" t="s">
+        <v>46</v>
+      </c>
+      <c r="E174">
+        <v>2</v>
+      </c>
+      <c r="G174">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>0</v>
+      </c>
+      <c r="B175">
+        <v>1420260191</v>
+      </c>
+      <c r="C175" s="1">
+        <v>46184</v>
+      </c>
+      <c r="D175" t="s">
+        <v>46</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="G175">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>0</v>
+      </c>
+      <c r="B176">
+        <v>1420260192</v>
+      </c>
+      <c r="C176" s="1">
+        <v>46185</v>
+      </c>
+      <c r="D176" t="s">
+        <v>46</v>
+      </c>
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="G176">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>0</v>
+      </c>
+      <c r="B177">
+        <v>1420260193</v>
+      </c>
+      <c r="C177" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D177" t="s">
+        <v>46</v>
+      </c>
+      <c r="E177">
+        <v>2</v>
+      </c>
+      <c r="G177">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>0</v>
+      </c>
+      <c r="B178">
+        <v>1420260194</v>
+      </c>
+      <c r="C178" s="1">
+        <v>46187</v>
+      </c>
+      <c r="D178" t="s">
+        <v>46</v>
+      </c>
+      <c r="E178">
+        <v>2</v>
+      </c>
+      <c r="G178">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>0</v>
+      </c>
+      <c r="B179">
+        <v>1420260195</v>
+      </c>
+      <c r="C179" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D179" t="s">
+        <v>46</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="G179">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>0</v>
+      </c>
+      <c r="B180">
+        <v>1420260196</v>
+      </c>
+      <c r="C180" s="1">
+        <v>46189</v>
+      </c>
+      <c r="D180" t="s">
+        <v>46</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>0</v>
+      </c>
+      <c r="B181">
+        <v>1420260197</v>
+      </c>
+      <c r="C181" s="1">
+        <v>46190</v>
+      </c>
+      <c r="D181" t="s">
+        <v>46</v>
+      </c>
+      <c r="E181">
+        <v>2</v>
+      </c>
+      <c r="G181">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>0</v>
+      </c>
+      <c r="B182">
+        <v>1420260198</v>
+      </c>
+      <c r="C182" s="1">
+        <v>46191</v>
+      </c>
+      <c r="D182" t="s">
+        <v>46</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>0</v>
+      </c>
+      <c r="B183">
+        <v>1420260199</v>
+      </c>
+      <c r="C183" s="1">
+        <v>46192</v>
+      </c>
+      <c r="D183" t="s">
+        <v>46</v>
+      </c>
+      <c r="E183">
+        <v>5</v>
+      </c>
+      <c r="G183">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>0</v>
+      </c>
+      <c r="B184">
+        <v>1420260200</v>
+      </c>
+      <c r="C184" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D184" t="s">
+        <v>46</v>
+      </c>
+      <c r="E184">
+        <v>2</v>
+      </c>
+      <c r="G184">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>0</v>
+      </c>
+      <c r="B185">
+        <v>1420260201</v>
+      </c>
+      <c r="C185" s="1">
+        <v>46194</v>
+      </c>
+      <c r="D185" t="s">
+        <v>46</v>
+      </c>
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="G185">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>0</v>
+      </c>
+      <c r="B186">
+        <v>1420260202</v>
+      </c>
+      <c r="C186" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D186" t="s">
+        <v>46</v>
+      </c>
+      <c r="E186">
+        <v>5</v>
+      </c>
+      <c r="G186">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>0</v>
+      </c>
+      <c r="B187">
+        <v>1420260203</v>
+      </c>
+      <c r="C187" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D187" t="s">
+        <v>46</v>
+      </c>
+      <c r="E187">
+        <v>4</v>
+      </c>
+      <c r="G187">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>0</v>
+      </c>
+      <c r="B188">
+        <v>1420260204</v>
+      </c>
+      <c r="C188" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D188" t="s">
+        <v>46</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>0</v>
+      </c>
+      <c r="B189">
+        <v>1420260205</v>
+      </c>
+      <c r="C189" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D189" t="s">
+        <v>46</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>0</v>
+      </c>
+      <c r="B190">
+        <v>1420260206</v>
+      </c>
+      <c r="C190" s="1">
+        <v>46199</v>
+      </c>
+      <c r="D190" t="s">
+        <v>46</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+      <c r="G190">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>0</v>
+      </c>
+      <c r="B191">
+        <v>1420260207</v>
+      </c>
+      <c r="C191" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D191" t="s">
+        <v>46</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>0</v>
+      </c>
+      <c r="B192">
+        <v>1420260208</v>
+      </c>
+      <c r="C192" s="1">
+        <v>46201</v>
+      </c>
+      <c r="D192" t="s">
+        <v>46</v>
+      </c>
+      <c r="E192">
+        <v>3</v>
+      </c>
+      <c r="G192">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>0</v>
+      </c>
+      <c r="B193">
+        <v>1420260209</v>
+      </c>
+      <c r="C193" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D193" t="s">
+        <v>46</v>
+      </c>
+      <c r="E193">
+        <v>3</v>
+      </c>
+      <c r="G193">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>0</v>
+      </c>
+      <c r="B194">
+        <v>1420260210</v>
+      </c>
+      <c r="C194" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D194" t="s">
+        <v>46</v>
+      </c>
+      <c r="E194">
+        <v>3</v>
+      </c>
+      <c r="G194">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>0</v>
+      </c>
+      <c r="B195">
+        <v>1420260211</v>
+      </c>
+      <c r="C195" s="1">
+        <v>46204</v>
+      </c>
+      <c r="D195" t="s">
+        <v>46</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="G195">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>0</v>
+      </c>
+      <c r="B196">
+        <v>1420260212</v>
+      </c>
+      <c r="C196" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D196" t="s">
+        <v>46</v>
+      </c>
+      <c r="E196">
+        <v>2</v>
+      </c>
+      <c r="G196">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>0</v>
+      </c>
+      <c r="B197">
+        <v>1420260213</v>
+      </c>
+      <c r="C197" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D197" t="s">
+        <v>46</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="G197">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>0</v>
+      </c>
+      <c r="B198">
+        <v>1420260214</v>
+      </c>
+      <c r="C198" s="1">
+        <v>46207</v>
+      </c>
+      <c r="D198" t="s">
+        <v>46</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="G198">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>0</v>
+      </c>
+      <c r="B199">
+        <v>1420260215</v>
+      </c>
+      <c r="C199" s="1">
+        <v>46208</v>
+      </c>
+      <c r="D199" t="s">
+        <v>46</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="G199">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>0</v>
+      </c>
+      <c r="B200">
+        <v>1420260216</v>
+      </c>
+      <c r="C200" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D200" t="s">
+        <v>46</v>
+      </c>
+      <c r="E200">
+        <v>2</v>
+      </c>
+      <c r="G200">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>0</v>
+      </c>
+      <c r="B201">
+        <v>1420260217</v>
+      </c>
+      <c r="C201" s="1">
+        <v>46210</v>
+      </c>
+      <c r="D201" t="s">
+        <v>46</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>0</v>
+      </c>
+      <c r="B202">
+        <v>1420260218</v>
+      </c>
+      <c r="C202" s="1">
+        <v>46211</v>
+      </c>
+      <c r="D202" t="s">
+        <v>46</v>
+      </c>
+      <c r="E202">
+        <v>3</v>
+      </c>
+      <c r="G202">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>0</v>
+      </c>
+      <c r="B203">
+        <v>1420260219</v>
+      </c>
+      <c r="C203" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D203" t="s">
+        <v>46</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
+      </c>
+      <c r="G203">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>0</v>
+      </c>
+      <c r="B204">
+        <v>1420260220</v>
+      </c>
+      <c r="C204" s="1">
+        <v>46213</v>
+      </c>
+      <c r="D204" t="s">
+        <v>46</v>
+      </c>
+      <c r="E204">
+        <v>2</v>
+      </c>
+      <c r="G204">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>0</v>
+      </c>
+      <c r="B205">
+        <v>1420260221</v>
+      </c>
+      <c r="C205" s="1">
+        <v>46214</v>
+      </c>
+      <c r="D205" t="s">
+        <v>46</v>
+      </c>
+      <c r="E205">
+        <v>1</v>
+      </c>
+      <c r="G205">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>0</v>
+      </c>
+      <c r="B206">
+        <v>1420260222</v>
+      </c>
+      <c r="C206" s="1">
+        <v>46215</v>
+      </c>
+      <c r="D206" t="s">
+        <v>46</v>
+      </c>
+      <c r="E206">
+        <v>4</v>
+      </c>
+      <c r="G206">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>0</v>
+      </c>
+      <c r="B207">
+        <v>1420260223</v>
+      </c>
+      <c r="C207" s="1">
+        <v>46216</v>
+      </c>
+      <c r="D207" t="s">
+        <v>46</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="G207">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>0</v>
+      </c>
+      <c r="B208">
+        <v>1420260224</v>
+      </c>
+      <c r="C208" s="1">
+        <v>46217</v>
+      </c>
+      <c r="D208" t="s">
+        <v>46</v>
+      </c>
+      <c r="E208">
+        <v>3</v>
+      </c>
+      <c r="G208">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>0</v>
+      </c>
+      <c r="B209">
+        <v>1420260225</v>
+      </c>
+      <c r="C209" s="1">
+        <v>46218</v>
+      </c>
+      <c r="D209" t="s">
+        <v>46</v>
+      </c>
+      <c r="E209">
+        <v>3</v>
+      </c>
+      <c r="G209">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>0</v>
+      </c>
+      <c r="B210">
+        <v>1420260226</v>
+      </c>
+      <c r="C210" s="1">
+        <v>46219</v>
+      </c>
+      <c r="D210" t="s">
+        <v>46</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>0</v>
+      </c>
+      <c r="B211">
+        <v>1420260227</v>
+      </c>
+      <c r="C211" s="1">
+        <v>46220</v>
+      </c>
+      <c r="D211" t="s">
+        <v>46</v>
+      </c>
+      <c r="E211">
+        <v>3</v>
+      </c>
+      <c r="G211">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>0</v>
+      </c>
+      <c r="B212">
+        <v>1420260228</v>
+      </c>
+      <c r="C212" s="1">
+        <v>46221</v>
+      </c>
+      <c r="D212" t="s">
+        <v>46</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+      <c r="G212">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>0</v>
+      </c>
+      <c r="B213">
+        <v>1420260229</v>
+      </c>
+      <c r="C213" s="1">
+        <v>46222</v>
+      </c>
+      <c r="D213" t="s">
+        <v>46</v>
+      </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
+      <c r="G213">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>0</v>
+      </c>
+      <c r="B214">
+        <v>1420260230</v>
+      </c>
+      <c r="C214" s="1">
+        <v>46223</v>
+      </c>
+      <c r="D214" t="s">
+        <v>46</v>
+      </c>
+      <c r="E214">
+        <v>4</v>
+      </c>
+      <c r="G214">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>0</v>
+      </c>
+      <c r="B215">
+        <v>1420260231</v>
+      </c>
+      <c r="C215" s="1">
+        <v>46224</v>
+      </c>
+      <c r="D215" t="s">
+        <v>46</v>
+      </c>
+      <c r="E215">
+        <v>5</v>
+      </c>
+      <c r="G215">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>0</v>
+      </c>
+      <c r="B216">
+        <v>1420260232</v>
+      </c>
+      <c r="C216" s="1">
+        <v>46225</v>
+      </c>
+      <c r="D216" t="s">
+        <v>46</v>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
+      <c r="G216">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>0</v>
+      </c>
+      <c r="B217">
+        <v>1420260233</v>
+      </c>
+      <c r="C217" s="1">
+        <v>46226</v>
+      </c>
+      <c r="D217" t="s">
+        <v>46</v>
+      </c>
+      <c r="E217">
+        <v>5</v>
+      </c>
+      <c r="G217">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>0</v>
+      </c>
+      <c r="B218">
+        <v>1420260234</v>
+      </c>
+      <c r="C218" s="1">
+        <v>46227</v>
+      </c>
+      <c r="D218" t="s">
+        <v>46</v>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+      <c r="G218">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>0</v>
+      </c>
+      <c r="B219">
+        <v>1420260235</v>
+      </c>
+      <c r="C219" s="1">
+        <v>46228</v>
+      </c>
+      <c r="D219" t="s">
+        <v>46</v>
+      </c>
+      <c r="E219">
+        <v>4</v>
+      </c>
+      <c r="G219">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>0</v>
+      </c>
+      <c r="B220">
+        <v>1420260236</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46229</v>
+      </c>
+      <c r="D220" t="s">
+        <v>46</v>
+      </c>
+      <c r="E220">
+        <v>3</v>
+      </c>
+      <c r="G220">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>0</v>
+      </c>
+      <c r="B221">
+        <v>1420260237</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46230</v>
+      </c>
+      <c r="D221" t="s">
+        <v>46</v>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>0</v>
+      </c>
+      <c r="B222">
+        <v>1420260238</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46231</v>
+      </c>
+      <c r="D222" t="s">
+        <v>46</v>
+      </c>
+      <c r="E222">
+        <v>4</v>
+      </c>
+      <c r="G222">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>0</v>
+      </c>
+      <c r="B223">
+        <v>1420260239</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46232</v>
+      </c>
+      <c r="D223" t="s">
+        <v>46</v>
+      </c>
+      <c r="E223">
+        <v>5</v>
+      </c>
+      <c r="G223">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>0</v>
+      </c>
+      <c r="B224">
+        <v>1420260240</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46233</v>
+      </c>
+      <c r="D224" t="s">
+        <v>46</v>
+      </c>
+      <c r="E224">
+        <v>5</v>
+      </c>
+      <c r="G224">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>0</v>
+      </c>
+      <c r="B225">
+        <v>1420260241</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46234</v>
+      </c>
+      <c r="D225" t="s">
+        <v>46</v>
+      </c>
+      <c r="E225">
+        <v>1</v>
+      </c>
+      <c r="G225">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>0</v>
+      </c>
+      <c r="B226">
+        <v>1420260242</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46235</v>
+      </c>
+      <c r="D226" t="s">
+        <v>46</v>
+      </c>
+      <c r="E226">
+        <v>5</v>
+      </c>
+      <c r="G226">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>0</v>
+      </c>
+      <c r="B227">
+        <v>1420260243</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46236</v>
+      </c>
+      <c r="D227" t="s">
+        <v>46</v>
+      </c>
+      <c r="E227">
+        <v>3</v>
+      </c>
+      <c r="G227">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>0</v>
+      </c>
+      <c r="B228">
+        <v>1420260244</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46237</v>
+      </c>
+      <c r="D228" t="s">
+        <v>46</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
+      <c r="G228">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>0</v>
+      </c>
+      <c r="B229">
+        <v>1420260245</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46238</v>
+      </c>
+      <c r="D229" t="s">
+        <v>46</v>
+      </c>
+      <c r="E229">
+        <v>3</v>
+      </c>
+      <c r="G229">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>0</v>
+      </c>
+      <c r="B230">
+        <v>1420260246</v>
+      </c>
+      <c r="C230" s="1">
+        <v>46239</v>
+      </c>
+      <c r="D230" t="s">
+        <v>46</v>
+      </c>
+      <c r="E230">
+        <v>2</v>
+      </c>
+      <c r="G230">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>0</v>
+      </c>
+      <c r="B231">
+        <v>1420260247</v>
+      </c>
+      <c r="C231" s="1">
+        <v>46240</v>
+      </c>
+      <c r="D231" t="s">
+        <v>46</v>
+      </c>
+      <c r="E231">
+        <v>4</v>
+      </c>
+      <c r="G231">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>0</v>
+      </c>
+      <c r="B232">
+        <v>1420260248</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46241</v>
+      </c>
+      <c r="D232" t="s">
+        <v>46</v>
+      </c>
+      <c r="E232">
+        <v>4</v>
+      </c>
+      <c r="G232">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>0</v>
+      </c>
+      <c r="B233">
+        <v>1420260249</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E233">
+        <v>5</v>
+      </c>
+      <c r="G233">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>0</v>
+      </c>
+      <c r="B234">
+        <v>1420260250</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46243</v>
+      </c>
+      <c r="D234" t="s">
+        <v>46</v>
+      </c>
+      <c r="E234">
+        <v>5</v>
+      </c>
+      <c r="G234">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>0</v>
+      </c>
+      <c r="B235">
+        <v>1420260251</v>
+      </c>
+      <c r="C235" s="1">
+        <v>46244</v>
+      </c>
+      <c r="D235" t="s">
+        <v>46</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>0</v>
+      </c>
+      <c r="B236">
+        <v>1420260252</v>
+      </c>
+      <c r="C236" s="1">
+        <v>46245</v>
+      </c>
+      <c r="D236" t="s">
+        <v>46</v>
+      </c>
+      <c r="E236">
+        <v>2</v>
+      </c>
+      <c r="G236">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>0</v>
+      </c>
+      <c r="B237">
+        <v>1420260253</v>
+      </c>
+      <c r="C237" s="1">
+        <v>46246</v>
+      </c>
+      <c r="D237" t="s">
+        <v>46</v>
+      </c>
+      <c r="E237">
+        <v>4</v>
+      </c>
+      <c r="G237">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>0</v>
+      </c>
+      <c r="B238">
+        <v>1420260254</v>
+      </c>
+      <c r="C238" s="1">
+        <v>46247</v>
+      </c>
+      <c r="D238" t="s">
+        <v>46</v>
+      </c>
+      <c r="E238">
+        <v>5</v>
+      </c>
+      <c r="G238">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>0</v>
+      </c>
+      <c r="B239">
+        <v>1420260255</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46248</v>
+      </c>
+      <c r="D239" t="s">
+        <v>46</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+      <c r="G239">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>0</v>
+      </c>
+      <c r="B240">
+        <v>1420260256</v>
+      </c>
+      <c r="C240" s="1">
+        <v>46249</v>
+      </c>
+      <c r="D240" t="s">
+        <v>46</v>
+      </c>
+      <c r="E240">
+        <v>4</v>
+      </c>
+      <c r="G240">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>0</v>
+      </c>
+      <c r="B241">
+        <v>1420260257</v>
+      </c>
+      <c r="C241" s="1">
+        <v>46250</v>
+      </c>
+      <c r="D241" t="s">
+        <v>46</v>
+      </c>
+      <c r="E241">
+        <v>2</v>
+      </c>
+      <c r="G241">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>0</v>
+      </c>
+      <c r="B242">
+        <v>1420260258</v>
+      </c>
+      <c r="C242" s="1">
+        <v>46251</v>
+      </c>
+      <c r="D242" t="s">
+        <v>46</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>0</v>
+      </c>
+      <c r="B243">
+        <v>1420260259</v>
+      </c>
+      <c r="C243" s="1">
+        <v>46252</v>
+      </c>
+      <c r="D243" t="s">
+        <v>46</v>
+      </c>
+      <c r="E243">
+        <v>2</v>
+      </c>
+      <c r="G243">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>0</v>
+      </c>
+      <c r="B244">
+        <v>1420260260</v>
+      </c>
+      <c r="C244" s="1">
+        <v>46253</v>
+      </c>
+      <c r="D244" t="s">
+        <v>46</v>
+      </c>
+      <c r="E244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>0</v>
+      </c>
+      <c r="B245">
+        <v>1420260261</v>
+      </c>
+      <c r="C245" s="1">
+        <v>46254</v>
+      </c>
+      <c r="D245" t="s">
+        <v>46</v>
+      </c>
+      <c r="E245">
+        <v>3</v>
+      </c>
+      <c r="G245">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>0</v>
+      </c>
+      <c r="B246">
+        <v>1420260262</v>
+      </c>
+      <c r="C246" s="1">
+        <v>46255</v>
+      </c>
+      <c r="D246" t="s">
+        <v>46</v>
+      </c>
+      <c r="E246">
+        <v>3</v>
+      </c>
+      <c r="G246">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>0</v>
+      </c>
+      <c r="B247">
+        <v>1420260263</v>
+      </c>
+      <c r="C247" s="1">
+        <v>46256</v>
+      </c>
+      <c r="D247" t="s">
+        <v>46</v>
+      </c>
+      <c r="E247">
+        <v>5</v>
+      </c>
+      <c r="G247">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>0</v>
+      </c>
+      <c r="B248">
+        <v>1420260264</v>
+      </c>
+      <c r="C248" s="1">
+        <v>46257</v>
+      </c>
+      <c r="D248" t="s">
+        <v>46</v>
+      </c>
+      <c r="E248">
+        <v>4</v>
+      </c>
+      <c r="G248">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>0</v>
+      </c>
+      <c r="B249">
+        <v>1420260265</v>
+      </c>
+      <c r="C249" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D249" t="s">
+        <v>46</v>
+      </c>
+      <c r="E249">
+        <v>4</v>
+      </c>
+      <c r="G249">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>0</v>
+      </c>
+      <c r="B250">
+        <v>1420260266</v>
+      </c>
+      <c r="C250" s="1">
+        <v>46259</v>
+      </c>
+      <c r="D250" t="s">
+        <v>46</v>
+      </c>
+      <c r="E250">
+        <v>4</v>
+      </c>
+      <c r="G250">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>0</v>
+      </c>
+      <c r="B251">
+        <v>1420260267</v>
+      </c>
+      <c r="C251" s="1">
+        <v>46260</v>
+      </c>
+      <c r="D251" t="s">
+        <v>46</v>
+      </c>
+      <c r="E251">
+        <v>4</v>
+      </c>
+      <c r="G251">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>0</v>
+      </c>
+      <c r="B252">
+        <v>1420260268</v>
+      </c>
+      <c r="C252" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D252" t="s">
+        <v>46</v>
+      </c>
+      <c r="E252">
+        <v>3</v>
+      </c>
+      <c r="G252">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>0</v>
+      </c>
+      <c r="B253">
+        <v>1420260269</v>
+      </c>
+      <c r="C253" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D253" t="s">
+        <v>46</v>
+      </c>
+      <c r="E253">
+        <v>4</v>
+      </c>
+      <c r="G253">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>0</v>
+      </c>
+      <c r="B254">
+        <v>1420260270</v>
+      </c>
+      <c r="C254" s="1">
+        <v>46263</v>
+      </c>
+      <c r="D254" t="s">
+        <v>46</v>
+      </c>
+      <c r="E254">
+        <v>2</v>
+      </c>
+      <c r="G254">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>0</v>
+      </c>
+      <c r="B255">
+        <v>1420260271</v>
+      </c>
+      <c r="C255" s="1">
+        <v>46264</v>
+      </c>
+      <c r="D255" t="s">
+        <v>46</v>
+      </c>
+      <c r="E255">
+        <v>2</v>
+      </c>
+      <c r="G255">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>0</v>
+      </c>
+      <c r="B256">
+        <v>1420260272</v>
+      </c>
+      <c r="C256" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D256" t="s">
+        <v>46</v>
+      </c>
+      <c r="E256">
+        <v>5</v>
+      </c>
+      <c r="G256">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>0</v>
+      </c>
+      <c r="B257">
+        <v>1420260273</v>
+      </c>
+      <c r="C257" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D257" t="s">
+        <v>46</v>
+      </c>
+      <c r="E257">
+        <v>3</v>
+      </c>
+      <c r="G257">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>0</v>
+      </c>
+      <c r="B258">
+        <v>1420260274</v>
+      </c>
+      <c r="C258" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D258" t="s">
+        <v>46</v>
+      </c>
+      <c r="E258">
+        <v>2</v>
+      </c>
+      <c r="G258">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>0</v>
+      </c>
+      <c r="B259">
+        <v>1420260275</v>
+      </c>
+      <c r="C259" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D259" t="s">
+        <v>46</v>
+      </c>
+      <c r="E259">
+        <v>1</v>
+      </c>
+      <c r="G259">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>0</v>
+      </c>
+      <c r="B260">
+        <v>1420260276</v>
+      </c>
+      <c r="C260" s="1">
+        <v>46269</v>
+      </c>
+      <c r="D260" t="s">
+        <v>46</v>
+      </c>
+      <c r="E260">
+        <v>5</v>
+      </c>
+      <c r="G260">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>0</v>
+      </c>
+      <c r="B261">
+        <v>1420260277</v>
+      </c>
+      <c r="C261" s="1">
+        <v>46270</v>
+      </c>
+      <c r="D261" t="s">
+        <v>46</v>
+      </c>
+      <c r="E261">
+        <v>2</v>
+      </c>
+      <c r="G261">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>0</v>
+      </c>
+      <c r="B262">
+        <v>1420260278</v>
+      </c>
+      <c r="C262" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D262" t="s">
+        <v>46</v>
+      </c>
+      <c r="E262">
+        <v>2</v>
+      </c>
+      <c r="G262">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>0</v>
+      </c>
+      <c r="B263">
+        <v>1420260279</v>
+      </c>
+      <c r="C263" s="1">
+        <v>46272</v>
+      </c>
+      <c r="D263" t="s">
+        <v>46</v>
+      </c>
+      <c r="E263">
+        <v>4</v>
+      </c>
+      <c r="G263">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>0</v>
+      </c>
+      <c r="B264">
+        <v>1420260280</v>
+      </c>
+      <c r="C264" s="1">
+        <v>46273</v>
+      </c>
+      <c r="D264" t="s">
+        <v>46</v>
+      </c>
+      <c r="E264">
+        <v>3</v>
+      </c>
+      <c r="G264">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>0</v>
+      </c>
+      <c r="B265">
+        <v>1420260281</v>
+      </c>
+      <c r="C265" s="1">
+        <v>46274</v>
+      </c>
+      <c r="D265" t="s">
+        <v>46</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
+      <c r="G265">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>0</v>
+      </c>
+      <c r="B266">
+        <v>1420260282</v>
+      </c>
+      <c r="C266" s="1">
+        <v>46275</v>
+      </c>
+      <c r="D266" t="s">
+        <v>46</v>
+      </c>
+      <c r="E266">
+        <v>3</v>
+      </c>
+      <c r="G266">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>0</v>
+      </c>
+      <c r="B267">
+        <v>1420260283</v>
+      </c>
+      <c r="C267" s="1">
+        <v>46276</v>
+      </c>
+      <c r="D267" t="s">
+        <v>46</v>
+      </c>
+      <c r="E267">
+        <v>5</v>
+      </c>
+      <c r="G267">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>0</v>
+      </c>
+      <c r="B268">
+        <v>1420260284</v>
+      </c>
+      <c r="C268" s="1">
+        <v>46277</v>
+      </c>
+      <c r="D268" t="s">
+        <v>46</v>
+      </c>
+      <c r="E268">
+        <v>2</v>
+      </c>
+      <c r="G268">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>0</v>
+      </c>
+      <c r="B269">
+        <v>1420260285</v>
+      </c>
+      <c r="C269" s="1">
+        <v>46278</v>
+      </c>
+      <c r="D269" t="s">
+        <v>46</v>
+      </c>
+      <c r="E269">
+        <v>1</v>
+      </c>
+      <c r="G269">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>0</v>
+      </c>
+      <c r="B270">
+        <v>1420260286</v>
+      </c>
+      <c r="C270" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D270" t="s">
+        <v>46</v>
+      </c>
+      <c r="E270">
+        <v>4</v>
+      </c>
+      <c r="G270">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>0</v>
+      </c>
+      <c r="B271">
+        <v>1420260287</v>
+      </c>
+      <c r="C271" s="1">
+        <v>46280</v>
+      </c>
+      <c r="D271" t="s">
+        <v>46</v>
+      </c>
+      <c r="E271">
+        <v>1</v>
+      </c>
+      <c r="G271">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>0</v>
+      </c>
+      <c r="B272">
+        <v>1420260288</v>
+      </c>
+      <c r="C272" s="1">
+        <v>46281</v>
+      </c>
+      <c r="D272" t="s">
+        <v>46</v>
+      </c>
+      <c r="E272">
+        <v>5</v>
+      </c>
+      <c r="G272">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>0</v>
+      </c>
+      <c r="B273">
+        <v>1420260289</v>
+      </c>
+      <c r="C273" s="1">
+        <v>46282</v>
+      </c>
+      <c r="D273" t="s">
+        <v>46</v>
+      </c>
+      <c r="E273">
+        <v>2</v>
+      </c>
+      <c r="G273">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>0</v>
+      </c>
+      <c r="B274">
+        <v>1420260290</v>
+      </c>
+      <c r="C274" s="1">
+        <v>46283</v>
+      </c>
+      <c r="D274" t="s">
+        <v>46</v>
+      </c>
+      <c r="E274">
+        <v>3</v>
+      </c>
+      <c r="G274">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>0</v>
+      </c>
+      <c r="B275">
+        <v>1420260291</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46284</v>
+      </c>
+      <c r="D275" t="s">
+        <v>46</v>
+      </c>
+      <c r="E275">
+        <v>2</v>
+      </c>
+      <c r="G275">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
